--- a/tabelas_classes_excel/Tabela_3-16_O_Paladino.xlsx
+++ b/tabelas_classes_excel/Tabela_3-16_O_Paladino.xlsx
@@ -1646,9 +1646,6 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr"/>
-    </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
@@ -2167,9 +2164,6 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-    </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -2177,9 +2171,6 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr"/>
-    </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
@@ -2194,18 +2185,12 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr"/>
-    </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
           <t>Sem a armadura pesada do guerreiro ou o</t>
         </is>
       </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -2246,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L257"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2299,31 +2284,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2335,56 +2295,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base de</t>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ataque</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fortitude</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reflexos</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vontade</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Especial</t>
+          <t>Aura do bem, detectar o mal, destruir o mal 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>2°</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2399,19 +2384,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aura do bem, detectar o mal, destruir o mal 1</t>
+          <t>Graça divina, cura pelas mãos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2421,34 +2406,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graça divina, cura pelas mãos</t>
+          <t>Aura de coragem, saúde divina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>4°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2463,26 +2448,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aura de coragem, saúde divina</t>
+          <t>Expulsar mortos-vivos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>+1</t>
@@ -2495,51 +2480,51 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Expulsar mortos-vivos</t>
+          <t>Destruir o mal 2/dia, montaria especial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>+6/+1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Destruir o mal 2/dia, montaria especial</t>
+          <t>Remover doença 1/semana</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2559,24 +2544,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Remover doença 1/semana</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2598,12 +2583,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2613,34 +2598,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Remover doença 2/semana</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2655,19 +2640,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Remover doença 2/semana</t>
+          <t>Destruir o mal 3/dia</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+10/+5</t>
+          <t>+11/+6/+1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2687,51 +2672,51 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Destruir o mal 3/dia</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+11/+6/+1</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Remover doença 3/semana</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+13/+8/+3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2751,24 +2736,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Remover doença 3/semana</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+13/+8/+3</t>
+          <t>+14/+9/+4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2790,12 +2775,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+14/+9/+4</t>
+          <t>+15/+10/+5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2805,34 +2790,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Remover doença 4/semana, destruir o mal 4/dia</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+15/+10/+5</t>
+          <t>+16/+11/+6/+1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2847,19 +2832,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Remover doença 4/semana, destruir o mal 4/dia</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+16/+11/+6/+1</t>
+          <t>+17/+12/+7/+2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2886,44 +2871,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+17/+12/+7/+2</t>
+          <t>+18/+13/+8/+3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Remover doença 5/semana</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+18/+13/+8/+3</t>
+          <t>+19/+14/+9/+4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2943,24 +2928,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Remover doença 5/semana</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+19/+14/+9/+4</t>
+          <t>+20/+15/+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2975,2320 +2960,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+20/+15/+10/+5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>Destruir o mal 5/dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um paladino (e a habilidade chave para cada perícia)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>paladino. Por exemplo, um paladino</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>são: Adestrar Animais (Car), Cavalgar (Des), Concentração (Con), Conhecimento</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>causaria 1d8+13 pontos de dano, ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>(nobreza e realeza) (Int), Conhecimento (religião) (Int), Cura (Sab), Diplomacia</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mágicos que normalmente se aplicam</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>(Car), Ofícios (Int), Profissão (Sab) e Sentir Motivação (Sab). Consulte o Capítulo</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>uma criatura que não seja maligna,</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>4; Perícias para obter as descrições das perícias.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ser utilizada novamente naquele di</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia no 1° nível: (2 + modificador de Inteligência) x 4.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>No 5° nível, e a cada cinco n</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia a cada nível subseqüente: 2 + modificador de Inteligên-</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>o mal uma vez adicional a cada dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cia.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>até o limite de cinco vezes por di</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Graça Divina (Sob): A partir</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Características da Classe</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>equivalente ao seu modificador de</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Usar Armas e Armaduras: Um paladino sabe usar todas as armas simples e</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>resistência.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>comuns, todos os tipos de armaduras (leves, médias e pesadas) e escudos (exceto</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Cura pelas Mãos (Sob): A part</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>escudo de corpo).</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>mais será capaz de curar ferimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Aura do Bem (Ext): O poder da aura do Bem de um paladino (consulte a</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>A cada dia, ele consegue recuperar</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>magia detectar o mal) equivale ao seu nível de paladino, semelhante à aura de um</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ao seu nível de paladino multiplic</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>clérigo de um deus Bom.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Por exemplo, um paladino de 7° nív</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Detectar o Mal (SM): O paladino pode usar detectar maldade sem limite</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>poderia curar 21 pontos de dano a</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>diário.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>entre diversos personagens, e não</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Destruir o Mal (Sob): Uma vez por dia, um paladino pode tentar destruir o</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>cura pelas mãos exige uma ação pad</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>mal usando um ataque corporal regular. Ele adiciona seu modificador de Carisma</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Por outro lado, o paladino é</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>(se houver) na jogada de ataque, causando 1 ponto de dano adicional por nível de</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>causar dano em mortos-vivos. Usar</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>à metade, ela não sofrerá qualquer dano</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>A MONTARIA DO PALADINO</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tência e metade do dano mesmo se fracas</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A montaria de um paladino é superior à uma montaria normal da mesma</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Partilhar Magias (Ext): O paladino</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>espécie e adquire poderes especiais, conforme descrito a seguir. A montaria (mas não uma habilidade similar à magia) co</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>padrão de um paladino Médio é um cavalo de guerra pesado e a montaria de taria. A criatura deve estar num raio de 1,5 m</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>um paladino Pequeno é um pônei de guerra (veja as estatísticas a seguir).</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>conjuração para receber os benefícios d</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>O Mestre e o jogador podem chegar a um acordo e escolher outro tipo efeito seja diferente de “instantânea”, ela de</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>de montaria, como um cachorro de montaria (para halflings) ou um tubarão ela se afastar do personagem (mais de 1,5 m) e</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Grande (para um paladino de uma campanha aquática). A montaria do pala- que retorne para a área de efeito da magia. Alé</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>dino deve ser considerada uma besta mágica, não um animal comum, para de conjurar qualquer magia que tenha alvo “Você”</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>todos os efeitos que dependam do seu tipo mas conserva os Dados de Vida, uma magia de toque à distância). Um paladino e</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>bônus base de ataque, testes de resistência, pontos de perícia e talentos do de partilhar magias mesmo que o efeito nor</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>animal).</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>do tipo da criatura (besta mágica).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Nível do</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>DV</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Armadura</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Testes de Resistência: A montaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Paladino Adicional Natural Força Int. Especial</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>sistência do paladino ou os valores da</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>5°-7°</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>6 Vinculo empático, evasão</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>utiliza seus próprios modificadores de</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>aprimorada, partilhar</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>não partilha outros bônus que o paladin</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>magias, partilhar testes de</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>por exemplo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>resistência</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Deslocamento Aprimorado (Ext): O d</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>8°-10°</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>7 Deslocamento aprimorado</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>em 3 m.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Comando (SM): Uma vez por dia a ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Comandar criaturas de sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>11°-14°</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>é capaz de comandar outro animal comum</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>espécie</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>pôneis de guerra essa categoria inclui</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>15°-20°</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>+10</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>9 Resistência à Magia</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>tidade inferior de Dados de Vida. Essa</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>mas a montaria deve obter sucesso em um</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Estatísticas Básicas: Use as estatísticas básicas para as criaturas da es- estiver em movimento durante a ativação</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>pécie, conforme descritas no Livro dos Monstros, com as alterações resumidas fracasse, a habilidade não funciona, mas a</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>na tabela acima e descritas a seguir.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>de utilizações diárias. O alvo deve obt</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>DV Adicional: Dados de Vida (d8) adicionais, que recebem os modificadores de Vontade (CD 10 + 1/2 nível do paladin</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>de Constituição normalmente. Lembre-se que os Dados de Vida adicionais paladino) para evitar o efeito.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>elevam o bônus base de ataque e os testes de Resistência da montaria. O</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Resistência à Magia (Ext): A Resis</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>bônus base de ataque de uma montaria é idêntico ao BBA de um clérigo 5 + nível do paladino. Para afetar a montaria com</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>com a mesma quantidade de Dados de Vida (ou seja, níveis) da criatura. Os radores precisam igualar ou superar a Resistê</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>testes de resistência de Fortitude e Reflexos do animal são bons (considere-o teste de conjurador (1d20 + nível do conj</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>um personagem com nível equivalente aos DV da criatura). Uma montaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>de paladino recebe perícias e talentos adicionais conforme o total de Dados</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>de Vida da criatura, semelhante a um monstro que recebeu uma progressão</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>EXEMPLOS DE MONTARIA DE PALADINO</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>As estatísticas a seguir pertencem</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>(veja Livro dos Monstros).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>da; elas não contêm os modificadores in</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Armadura Natural: O valor indicado é adicionado à armadura natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cavalo de Guerra Pesado: ND 2; ani</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>existente da criatura e representa a resistência sobrenatural da montaria do</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>+1; Desl.: 15 m; CA 14, toque 10, surpr</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>paladino.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>corpo: casco +6 (dano: 1d6+4); Ataque T</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Força: Adicione o bônus indicado aos valores de Força da montaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>(dano: 1d6+4) e mordida (dano: 1d4+3);</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Int.: O valor de Inteligência da montaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>na penumbra, faro; TR Fort +7, Ref +5,</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Vinculo Empático (Ext): O paladino possui um Vinculo Empático com sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sab 13, Car 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>montaria com 1,5 km de alcance máximo. Ele não é capaz de enxergar através</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Perícias e Talentos: Observar +4,</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>dos olhos do animal, mas pode se comunicar por telepatia com a criatura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Pônei de Guerra: ND 1/3; animal Mé</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Note que mesmo as montarias inteligentes compreendem o mundo de for-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>12 m; CA 13, toque 11, surpresa 12; BBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ma diferente dos humanos, portanto são possíveis falhas de interpretação</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>+3 (dano: 1d3+2); Ataque Total: Corpo a</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>(consulte Familiares).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Espaço/Alcance 1,5 m/l ,5 m ; QE: visão</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Devido ao vinculo empático, o paladino compartilha a mesma conexão</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Von+0; For 15, Des 13, Con 14, Int 2, S</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>com itens ou locais que a montaria, semelhante a um conjurador e seu familiar</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Perícias e Talentos: Observar +5,</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>(consulte Familiares).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Consulte o Livro do Mestre para ob</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Evasão Aprimorada (Ext): Sempre que a montaria se tornar alvo de um</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>de estatísticas das criaturas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ataque que permita um teste de resistência de Reflexos para reduzir o dano</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>de toque bem-sucedido que não provoca ataques de oportunidade. O paladino</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Ex-Paladinos</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>decide quantos pontos de seu limite diário utilizará depois de tocar com sucesso</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Um paladino que abandone</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>o morto-vivo.</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>voluntariamente ou viole de mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Aura de Coragem (Sob): A partir do 3° nível, um paladino será imune ao medo</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>magias e habilidades especiais</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>(mágico ou não). Qualquer aliado que se encontre num raio de 3 m do paladino</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>talentos com armas, armaduras</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>recebe +4 de bônus de moral em todos os testes de resistência contra efeitos de medo.</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Ele não conseguirá adquir</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Essa habilidade funciona enquanto o paladino estiver consciente, mas não quando</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>habilidades e seu acesso aos n</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>estiver inconsciente ou morto.</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>descrição da magia penitência)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Saúde Divina (Ext): A partir do 3° nível, um paladino adquire imunidade</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Semelhante aos integrante</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>contra todas as doenças, inclusive as doenças sobrenaturais e mágicas (como a</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>personagem multiclasse, mas ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>podridão da múmia e a licantropia).</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>uma nova classe ou (caso seja</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Expulsar Mortos-Vivos (Sob): Quando um paladino atinge o 4° nível, ele</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>aumentar seu nível de paladino</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>adquire a habilidade sobrenatural de expulsar mortos-vivos. Ele pode usar essa</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>adquiridas anteriormente. O ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>habilidade uma quantidade de vezes por dia equivalente a 3 + seu modificador de</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Quando alguém adota essa class</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Carisma. Ele expulsa mortos-vivos como um clérigo com três níveis abaixo do seu</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Uma vez que se afaste do camin</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>nível de paladino (veja Expulsar e Fascinar Mortos-Vivos).</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Magias: A partir do 4° nível, um paladino adquire a habilidade de conjurar uma</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>pequena quantidade de magias divinas (o mesmo tipo de magias disponíveis para</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Conjunto Inicial para Paladino</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Armadura: Brunea (+4 CA,</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>clérigos, druidas e rangers), que estão relacionadas na lista de magias do paladino.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>mento, 15 kg).</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Ele precisa escolher e preparar suas magias com antecedência.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Escudo grande de madeira</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Para preparar e conjurar uma magia, um paladino deve ter uma pontuação</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Armas: Espada longa (1d8,</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>em Sabedoria igual ou superior a 10 + o nível da magia (Sab 11 para magias de 1°</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Arco Curto (1d6, dec.x 3,</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>nível, Sab 12 para magias de 2° nível e assim por diante). A Classe de Dificuldade</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Seleção de Perícias: Esco</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>para os testes de resistência contra essas magias equivale a 10 + nível da magia +</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>a 3 + modificador de Inteligên</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>modificador de Sabedoria do paladino.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Semelhante aos demais conjuradores, um paladino somente é capaz de conju-</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Perícia</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Gradu</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>rar uma quantidade limitada de magias de cada nível por dia. Seu limite diário de</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>magias se encontra na Tabela 3-16:0 Paladino. As magias adicionais do paladino são</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Cavalgar</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>baseadas em um valor elevado de Sabedoria (consulte a Tabela 1-1: Modificadores das</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Escalar (oc)</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Habilidades e Magias Adicionais). Quando a Tabela 3-16 indicar que um paladino</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Observar (oc)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>recebe 0 magias de um determinado nível (por exemplo, 0 magias de 1° nível para</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Cura</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>um paladino de 4° nível), ele recebe somente as magias adicionais concedidas pelo</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Diplomacia</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>seu valor de Sabedoria para aquele nível. O paladino não tem acesso a nenhum</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Ouvir (oc)</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>domínio ou poderes concedidos, como os clérigos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Um paladino prepara e conjura magias da mesma forma que um clérigo, embora</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Procurar (oc)</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>não consiga eliminar uma magia preparada e convertê-la em um efeito de curar. Ele</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>consegue preparar e conjurar qualquer magia da lista de magias do paladino, limitado</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Talento: Foco em Arma (es</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>pelos níveis de magia que o personagem é capaz de conjurar, mas deve escolher suas</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Talento Adicional: Inicia</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>magias com antecedência, durante a sua meditação diária.</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Equipamento: Mochila com</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Até o 3° nível, o paladino não terá nível de conjurador. A partir do 4° nível, seu</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>saco, pederneira e isqueiro. L</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>nível de conjurador equivale à metade de seu nível de paladino.</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Símbolo sagrado de madeira (pu</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Montaria Especial (SM): Ao atingir o 5° nível, o paladino recebe os serviços de</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Dinheiro: 6d4 PO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>uma montaria sobrenatural, inteligente, forte e leal, que o auxiliará em sua cruzada</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>contra o mal (veja o quadro Montaria de Paladino). Essa montaria normalmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>é um cavalo de guerra pesado (para paladinos Médios) ou um pônei de guerra</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>(paladinos Pequenos).</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Uma vez por dia, usando uma ação de rodada completa, um paladino é ca-</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>As florestas e as colinas</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>paz de invocar a montaria do reino celestial onde ela reside. A montaria aparece</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>nários ursos-coruja e as malic</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>imediatamente ao lado dele e permanece no Plano Material durante 2 horas por</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>poderoso e perspicaz que essas</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>nível do paladino; ela pode ser dispensada a qualquer hora como uma ação livre. A</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>floresta como se ela fosse sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>montaria será a mesma criatura sempre que for invocada, embora o paladino seja</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>capaz de liberar um animal específico (se ele estiver muito velho para juntar-se à</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Aventuras: Muitas vezes,</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>sua cruzada, por exemplo). Toda vez que ela é invocada, aparece sem ferimentos,</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>todos que habitam ou viajam pe</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>independente de qualquer dano sofrido anteriormente. Ela também aparece usando</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>espécies de criaturas e não de</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>ou carregando qualquer equipamento que tinha quando foi dispensada pela última</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Ele também pode se aventurar p</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>vez (incluindo armadura de montaria, sela, alforje, etc.). Invocar uma montaria é</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Características: Um range</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>um efeito de conjuração (convocação).</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>bate. Suas perícias lhe permit</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Se a montaria de um paladino perecer, ela desaparecerá imediatamente, deixando</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>todo equipamento que carregava. O paladino não pode invocar outra montaria du-</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>ser rastreado. Ele possui conh</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>rante trinta dias ou até adquirir um nível de classe, o que ocorrer primeiro, mesmo</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>tornando-o mais eficaz para en</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>que a montaria de alguma forma seja ressuscitada. Durante esse período de trinta</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>ranger experiente desenvolve u</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>dias, o paladino sofre -1 de penalidade nas jogadas de ataque e dano.</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>de extrair o poder da terra e</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Remover Doenças (SM): A partir do 6° nível, um paladino é capaz de remover</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Tendência: Os rangers pod</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>doenças, com efeitos similares à magia remover doenças uma vez por semana. Ele</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Bons e se dedicam à proteção d</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>pode usar essa habilidade uma vez adicional por semana a cada três níveis depois do</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>6° (duas vezes por semana no 9° nível, três vezes no 12° e assim por diante).</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>criaturas malignas que ameaçam</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Código de Conduta: Um paladino deve manter a tendência Leal e Bom e</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>os viajantes, servindo como gu</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>perderá todas as habilidades especiais de classe se cometer um ato maligno volun-</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>preferindo obedecer ao fluxo d</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>tariamente. Além disso, o código do paladino exige que ele respeite as autoridades</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>regras inflexíveis. Embora sej</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>legítimas, aja com honra (não mentir, não roubar, não usar venenos, etc.), ajude</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>observam a crueldade da nature</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>as pessoas em necessidade (desde que essa ajuda não tenha objetivos caóticos ou</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Eles adquirem magias divinas c</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>malignos) e traga justiça às criaturas que ferem ou ameaçam os inocentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>não significam nada para a nat</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Companheiros: Os paladinos podem se aventurar com personagens de qualquer</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>tendência Neutra ou Bondosa, mas jamais se aliará a uma criatura maligna e nem</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Religião: Embora os ranger</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>permanecerá ao lado de alguém que viole constantemente seu código moral. Um</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>venerar uma divindade como os</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>paladino só pode contratar homens ou aceitar seguidores que sejam Leais e Bons.</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>e Obad-Hai (deus da natureza)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>ainda que determinados indivíd</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>História: Alguns rangers receberam seu treinamento como parte das tropas</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>dos rangers utiliza seus companh</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>especiais de algum exército, mas a maioria adquiriu suas habilidades com mestres</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>auxiliá-los em combate corporal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>solitários, que os aceitaram como estudantes e ajudantes. Os rangers do mesmo</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>INFORMAÇÕES DE JOGO</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>mestre podem se considerar companheiros ou rivais, lutando pelo status de melhor</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Os rangers possuem as seguin</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>estudante e herdando a fama do mestre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Habilidades: A Destreza é e</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Raças: Com freqüência, os elfos escolhem o caminho do ranger. Eles se sentem</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>de armaduras leves e em função d</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>confortáveis nas florestas e possuem a graciosidade necessária para se mover furti-</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>de. A Força é importante, pois o</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>vamente. Os meio-elfos que herdam a ligação com a floresta de seus pais élficos</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>também escolhem essa classe. Os humanos se tornam excelentes rangers, pois</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Soveliss</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>são adaptáveis o suficiente para aprender os caminhos da floresta, ainda que</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>não possuam um dom racial. Os meio-orcs consideram a vida do ranger mais</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>confortável e cômoda que a vida entre os cruéis e incômodos humanos (ou</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>orcs). Os rangers gnomos são mais comuns que os guerreiros gnomos,</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>míni</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>mas eles costumam permanecer em suas terras em vez de se aventurar</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>de ran</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>entre o “povo alto”. Os rangers anões são raros, mas podem ser muito</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Tend</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>eficazes. Em vez de viver nas florestas da superfície, eles habitam as</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Dad</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>intermináveis cavernas subterrâneas. Nelas, caçam e destroem os</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>inimigos de sua raça com a precisão incansável que os tornaram</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Perícia</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>famosos. Os rangers anões são mais conhecidos como “ca-</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>verneiros”. Os rangers halflings são muito respeitados</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>chave</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>por sua habilidade em ajudar as comunidades</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>da raça a prosperar enquanto prosseguem em</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>(Co</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>seu modo de vida nômade.</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>(m</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Entre os humanóides selvagens, os ran-</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>gers são comuns entre os gnolls, que utilizam</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>as habilidades da classe para caçar sua presa</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>com sagacidade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Outras Classes: Os rangers conservam</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>(</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>boas relações com os druidas e, até certo pon-</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>to, com os bárbaros. Eles são famosos por</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>gerar desentendimentos com os paladinos,</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>principalmente porque ambos têm objetivos</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>similares, mas diferem em estilos, táticas, filosofia</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>mo</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>e estética. Como os rangers não procuram dire-</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>tamente por apoio ou amizade, é simples tolerar as</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>pessoas que são diferentes, como os magos estudiosos</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>e os clérigos pregadores. Eles simplesmente não se</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>importam com as diferenças alheias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Função: A melhor função para um</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>ranger será batedor e segundo em combate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Sem a armadura pesada do guerreiro ou o</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>vigor dos bárbaros, o ranger poderia se concen-</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>rela</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>trar no oportunismo e nos ataques à distância. A maioria</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Range</t>
         </is>
       </c>
     </row>
